--- a/survey_templates/048_energy_drink_consumption_survey--survey_templates.xlsx
+++ b/survey_templates/048_energy_drink_consumption_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -538,46 +538,46 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>energy_drink_consumption</t>
+          <t>energy_drink_type</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Energy Drink Consumption</t>
+          <t>Energy Drink Type</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>side_effects</t>
+          <t>frequency_of_consumption</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Side Effects</t>
+          <t>Frequency of Consumption</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>perceptions</t>
+          <t>amount_of_consumption</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Perceptions</t>
+          <t>Amount of Consumption</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>demographics_2</t>
+          <t>side_effects</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Demographics 2</t>
+          <t>Side Effects</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>side_effects_2</t>
+          <t>perceptions</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Side Effects 2</t>
+          <t>Perceptions</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>energy_drink_consumption_2</t>
+          <t>survey_completion</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Energy Drink Consumption 2</t>
+          <t>Survey Completion</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>survey_completion</t>
+          <t>demographics_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Survey Completion</t>
+          <t>Additional Information</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>demographics_3</t>
+          <t>side_effects_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Demographics 3</t>
+          <t>Additional Side Effects</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>side_effects_2</t>
+          <t>energy_drink_consumption_frequency</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Side Effects 2</t>
+          <t>Energy Drink Consumption Frequency</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>energy_drink_consumption_3</t>
+          <t>amount_of_consumption_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Energy Drink Consumption 3</t>
+          <t>Energy Drink Amount</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -778,203 +778,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Survey Completion 2</t>
+          <t>Thank You</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>perceptions_2</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Perceptions 2</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>energy_drink_type</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Energy Drink Type</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>What type of energy drink do you typically consume? (e.g., Red Bull, Monster, Rockstar)</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>frequency_of_consumption</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Frequency of Consumption</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>amount_of_consumption</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Amount of Consumption</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>side_effects</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Side Effects</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>perceptions</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Perceptions</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>survey_completion_3</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Survey Completion 3</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>energy_drink_consumption_frequency</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>How often do you consume energy drinks?</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Please select frequency of consumption</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -991,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1019,253 +827,406 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>side_effects_choices</t>
+          <t>energy_drink_type_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>headaches</t>
+          <t>red_bull</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Headaches</t>
+          <t>Red Bull</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>side_effects_choices</t>
+          <t>energy_drink_type_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>insomnia</t>
+          <t>monster</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Insomnia</t>
+          <t>Monster</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>side_effects_choices</t>
+          <t>energy_drink_type_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nausea</t>
+          <t>rockstar</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Nausea</t>
+          <t>Rockstar</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>side_effects_choices</t>
+          <t>energy_drink_type_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>fatigue</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Fatigue</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>side_effects_choices</t>
+          <t>frequency_of_consumption_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>heart_palpitations</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Heart palpitations</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>side_effects_choices</t>
+          <t>frequency_of_consumption_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>stomach_problems</t>
+          <t>less_than_once_a_week</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Stomach problems</t>
+          <t>Less than once a week</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>side_effects_choices</t>
+          <t>frequency_of_consumption_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>muscle_weakness</t>
+          <t>about_once_a_week</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Muscle weakness</t>
+          <t>About once a week</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>side_effects_choices</t>
+          <t>frequency_of_consumption_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>several_times_a_week</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Several times a week</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>perceptions_choices</t>
+          <t>frequency_of_consumption_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>every_day</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Every day</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>perceptions_choices</t>
+          <t>side_effects_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>headaches</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Headaches</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>energy_drink_consumption_frequency_choices</t>
+          <t>side_effects_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>insomnia</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>Insomnia</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>energy_drink_consumption_frequency_choices</t>
+          <t>side_effects_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>less_than_once_a_week</t>
+          <t>nausea</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Less than once a week</t>
+          <t>Nausea</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>energy_drink_consumption_frequency_choices</t>
+          <t>side_effects_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>about_once_a_week</t>
+          <t>fatigue</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>About once a week</t>
+          <t>Fatigue</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>energy_drink_consumption_frequency_choices</t>
+          <t>side_effects_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>several_times_a_week</t>
+          <t>heart_palpitations</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Several times a week</t>
+          <t>Heart palpitations</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>side_effects_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>stomach_problems</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Stomach problems</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>side_effects_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>muscle_weakness</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Muscle weakness</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>side_effects_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>other_(please_specify)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Other (please specify)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>perceptions_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>perceptions_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>energy_drink_consumption_frequency_choices</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>never</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>energy_drink_consumption_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>less_than_once_a_week</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Less than once a week</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>energy_drink_consumption_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>about_once_a_week</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>About once a week</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>energy_drink_consumption_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>several_times_a_week</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Several times a week</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>energy_drink_consumption_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
         <is>
           <t>every_day</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Every day</t>
         </is>
